--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542047</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,6 +891,236 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136547464</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136950127</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99355</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kogsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>494019</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7030824</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950127</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136950128</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99355</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kogsta, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>494001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7030840</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950128</t>
         </is>
       </c>
     </row>
@@ -898,6 +1128,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542047</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542047</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136547464</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16336-2025 artfynd.xlsx
+++ b/artfynd/A 16336-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136950127</v>
       </c>
       <c r="B4" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136950128</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
